--- a/光伏配储项目/电价数据/2026/白藤站.xlsx
+++ b/光伏配储项目/电价数据/2026/白藤站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55377</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.92623</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.06426</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.9857899999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.81179</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.81936</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.57755</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.62995</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.56314</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.78923</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.78931</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.7816799999999999</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.55643</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.80332</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.79564</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.76634</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.78651</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.57538</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.79787</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.58528</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.7963300000000001</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.80336</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.59835</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.82825</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.91612</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.86599</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.68174</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.67669</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7402300000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7630800000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.02059</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.0063</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.09742</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75306</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7046</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50314</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.78607</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9595499999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.32207</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52522</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.76655</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.77454</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.75252</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.93711</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.90296</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.05572</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.32539</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.1459</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.15517</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7380399999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.22215</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.17643</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09926</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.23598</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53891</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.14029</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.25708</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.48264</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.31461</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.24237</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41844</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.36116</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.29224</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80724</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.17457</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03947</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17815</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5135599999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.6531</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.62741</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.53262</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.5791900000000001</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.5528500000000001</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.56101</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.56098</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.55289</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.5540700000000001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.60575</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.83492</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.15115</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.6309400000000001</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5246000000000001</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.58047</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.94224</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.15724</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.78239</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.12286</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.04367</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.99642</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.71299</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56996</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.68475</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.16622</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.24032</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.48593</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.16824</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.08224</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8254400000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25858</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.14497</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28686</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62285</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.64218</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6233500000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.17426</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.17761</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.18599</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.18017</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.97729</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18653</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20142</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19439</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67075</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.17132</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20621</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.22494</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5217</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.42971</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.17729</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50865</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26462</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7466499999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7645599999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91501</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.73776</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.73552</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.5569700000000001</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.61238</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.53643</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.9906200000000001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.66737</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.65918</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.62402</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.59989</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.53914</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.6575800000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.61052</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.54914</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.59576</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.5467000000000001</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.5515800000000001</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.54847</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.55637</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.5013299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69682</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83312</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11119</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87591</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7507999999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.7061000000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60577</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64252</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7335700000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16971</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.53238</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.68231</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.17387</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.63464</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18986</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79715</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.94898</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.17397</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.17503</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89651</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67574</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.17171</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.03511</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.17395</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.40559</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.24841</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.17463</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21775</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21077</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.41394</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.27524</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.29167</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.65421</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.18347</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.18495</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.04754</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.08504</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.1059</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.09196</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.21384</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.17541</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.25752</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.00269</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75849</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71526</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53244</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.12875</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.75544</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.44196</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.72249</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.89528</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5805399999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.53233</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.6547500000000001</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.57352</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.7190800000000001</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.6592899999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5986399999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.56367</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.55852</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.49557</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.46107</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.5616100000000001</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.56752</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.64213</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.54612</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.5342100000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.49783</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.50225</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6792699999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71992</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9352</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.17533</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.31718</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.84465</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55955</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66757</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90613</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8726</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.17085</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44176</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77435</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.96239</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.21641</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.6945800000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12126</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5245599999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6584500000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.00404</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10917</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.25355</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.17669</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.07156</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.9907899999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02821</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9921599999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.26361</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.45074</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79874</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.35768</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.43546</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.20262</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.85248</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.08276</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16773</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12492</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.16341</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.26305</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.32569</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.16339</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.2776</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.19205</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18757</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18602</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.19596</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.19962</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.18519</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.16261</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17966</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72894</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7316900000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32172</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7453200000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47953</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5063</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52497</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45791</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45684</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.85145</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.61753</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70473</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72988</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70824</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5531900000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5949800000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08975</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55157</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51513</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63761</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48542</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48956</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5980700000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50754</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50756</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19841</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9741299999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9897699999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59268</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.67762</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.59656</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5690499999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.57002</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.78688</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.58241</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.58265</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.56896</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.56971</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.57029</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07378</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04568999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08315</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12936</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04661999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44663</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.63466</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.59178</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.60922</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.59329</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.59265</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33439</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.59976</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.50875</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27234</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74775</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.88159</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67977</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.65376</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6722899999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7537699999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.94662</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.73433</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73634</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.89462</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6461399999999999</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5390199999999999</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08776</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73521</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.73412</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.64301</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60594</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.73156</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7892899999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78492</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60314</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7450800000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02144</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.41285</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8479</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.44111</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.31098</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7949299999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.05034</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40777</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.77135</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44963</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77777</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8005599999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7851699999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8788899999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50214</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41159</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46028</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2187</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54128</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.65576</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.62693</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.6113500000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.61809</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.62342</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.62466</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.60861</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.52395</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.51998</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.59393</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.57202</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.5740299999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.57128</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5716100000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5999800000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.57241</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.6055900000000001</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.5106499999999999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.6241100000000001</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.52398</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43731</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5639700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66643</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07923</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6409199999999999</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5043500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57129</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59818</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00356</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33992</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30781</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27433</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55975</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8013400000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5739299999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65234</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55267</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.96515</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77944</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7284299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64458</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5775399999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.9789500000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54965</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.68935</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.69684</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6818</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.74486</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.66334</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.68055</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5903200000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5815900000000001</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.70185</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.65859</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.6968799999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.7109800000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.76749</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.70377</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.76839</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.7105199999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.7111900000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6977100000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.68945</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6567799999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.68889</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.64361</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.59509</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.64813</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.60477</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.6243300000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.60593</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.59437</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.58623</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.50803</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95611</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.61049</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.6778200000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.67798</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.7349600000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.58468</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.59604</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.5405599999999999</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5700700000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.52397</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64773</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51839</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6209600000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.73377</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.12277</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9346599999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5491900000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11667</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8501599999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9565900000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.86627</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6435700000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.81663</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.0754</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52554</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43378</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.88282</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.04119</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.62866</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.20281</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.79018</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.82023</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.78338</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7453200000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47591</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49979</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19731</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51404</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7958999999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7546900000000001</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.17265</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92499</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64708</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.71284</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70462</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.56121</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16761</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61852</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.91284</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5829800000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.61966</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.37868</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.3029</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.27076</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.44296</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.05071</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.52516</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6059099999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.51194</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.08134</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07951</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.91861</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9863999999999999</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9401</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17744</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.16244</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.16339</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.6139</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9777400000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.02262</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.16296</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.95774</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99819</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.59091</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.9311499999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.9883500000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.09581</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.89254</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.88017</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79973</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.10392</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.57101</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.96696</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99988</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74734</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33407</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.66631</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.54261</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.54513</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.47627</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.58541</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.6646599999999999</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.5517000000000001</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.54612</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.5320900000000001</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.57648</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8337899999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7170599999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.6204400000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.60848</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.82451</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.9890399999999999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.61063</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.55111</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.60181</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.67615</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.61054</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.48908</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.49907</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.50141</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.68206</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.54844</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5498200000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.54523</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.54734</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.57692</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.49563</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.63755</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5830700000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.58833</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.5781000000000001</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.6031299999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.53373</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.47152</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.55596</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5805900000000001</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.5832200000000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.57335</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.52844</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.51835</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55532</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48567</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70233</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60372</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6274</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84849</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27054</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16557</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8516900000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70108</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93967</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16718</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12094</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01779</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54169</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49707</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44633</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56391</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.49973</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.49974</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.55806</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.42333</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.47108</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.5227200000000001</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.56175</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.54567</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.6182300000000001</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.81333</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.15204</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.15369</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99386</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98258</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.9841299999999999</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56466</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54853</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94564</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08553</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78627</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01254</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77027</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65084</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64357</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71087</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79918</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29743</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.79453</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.38374</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.18186</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.00869</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.67628</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62627</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65991</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67328</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66835</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64533</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66982</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20685</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70275</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78454</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70005</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70783</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71598</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63535</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75028</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02097</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13065</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69389</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70233</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.6961</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77573</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72589</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81521</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6680199999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46359</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.10868</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.50442</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.6182000000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.49472</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.5277200000000001</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.4891</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.63822</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.21738</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.55622</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.52854</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.57051</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5567799999999999</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.55288</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.49903</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.48079</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42581</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7489400000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49517</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.5115299999999999</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92447</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47713</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18245</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.9017200000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7627699999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50025</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4982799999999999</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7485299999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42669</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51593</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68677</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49668</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42218</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66603</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.56129</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.52635</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.5214299999999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.81976</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.5097200000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43911</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51625</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7610399999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7676799999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48079</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54591</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50142</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72229</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76205</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55389</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50162</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01985</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48589</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44581</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.0939</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12904</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11191</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12843</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01826</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19404</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14231</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13144</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.1747</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84151</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19109</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84834</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34088</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9031399999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.7265</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75725</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94845</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.43376</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.68579</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5804600000000001</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.56941</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.59058</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.49621</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75718</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.4363</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.55543</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.68457</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.67777</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.56823</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.5505399999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.63781</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.65358</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.65577</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.55952</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.6558099999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.57065</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.64088</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.48645</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.49324</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4932</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.53422</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5159199999999999</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.66471</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.56401</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.72327</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.56328</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.04979</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.78032</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7467200000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.28521</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34641</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.72455</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64763</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.35352</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.99751</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59687</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49517</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49633</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54179</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5925900000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73825</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.18342</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.69499</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91947</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.66903</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9411499999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.88698</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74996</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71936</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17817</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17935</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.43187</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.24369</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.62935</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.21644</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28566</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.08666</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.40878</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.0354</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.73197</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.6949299999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43426</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.18283</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.64723</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45711</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52724</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5327000000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80028</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6726599999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.65419</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50729</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.07272</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.67334</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66386</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.05771</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.1745</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19398</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15485</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55691</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5714600000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42777</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23473</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42968</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47976</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5112</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5396299999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59975</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75764</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.1307</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.72778</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.59774</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49514</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58329</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46254</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46363</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5477300000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.53637</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.51564</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.52034</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.53844</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37609</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.9014099999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.52858</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.48159</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.47525</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.47017</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23372</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.12324</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.70992</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.18488</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.11006</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69148</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.56133</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49398</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.55137</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80396</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48606</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09594</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.37137</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9204199999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.86413</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52289</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7553200000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75425</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55567</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.54886</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.85714</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6130800000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.79922</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75507</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.32642</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.32978</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.22449</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06879</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.96314</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.29329</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61799</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.54647</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.75288</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5434500000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.2201</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75603</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75413</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5778300000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44943</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.99313</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.76302</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.62107</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75329</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.18148</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6029800000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.73365</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62836</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.24515</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.88113</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.86627</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.90608</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15941</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.64216</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.93929</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.68323</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.96454</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.63054</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.64885</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.74244</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.63102</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24948</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03702</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.00399</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.01552</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.52388</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34746</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7556900000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34532</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55763</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80301</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55057</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75259</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75439</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42846</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42227</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6305499999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59187</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55852</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55808</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81208</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.16017</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.1231</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03601</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12582</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.73236</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72711</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04684</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06521</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6726599999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55522</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56168</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5529400000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47799</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46988</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5473600000000001</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5511699999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54563</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04582</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54761</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49829</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48121</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48095</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55589</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5594600000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49663</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51237</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49907</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5593400000000001</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.65842</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15877</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.06187</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6594800000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58102</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15485</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8657100000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6588099999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14664</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.8198300000000001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51032</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5335800000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34439</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.7827999999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.6194299999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6263099999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.8231900000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.59516</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.46179</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6269600000000001</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5851900000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.63317</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.01205</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.18627</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92698</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96829</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01686</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.9585199999999999</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.92515</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.95524</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.93886</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.92257</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9249400000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.71113</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.07102</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6889700000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.06767</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.16504</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.14689</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.70696</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92911</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.84977</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9166799999999999</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54387</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.67341</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.69591</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.7443</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.79434</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.20075</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.08092</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.02047</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.33278</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01606</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11511</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91964</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75515</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7543800000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8160299999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5607000000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68951</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72917</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68914</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.75075</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6992699999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46227</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7376900000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50692</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.00276</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.9000199999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.01519</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.90628</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.02301</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.00584</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.00603</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.21146</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.07545</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.13787</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.47982</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66983</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.60354</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.72323</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.7097599999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02494</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.70465</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75768</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13882</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.27446</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.47905</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.41002</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.0259</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.4477</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.42696</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.79091</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.70132</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.46882</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.47063</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80898</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75889</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8037300000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6115499999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.43917</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7557699999999999</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43949</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49854</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.81045</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00327</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9333899999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95961</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03455</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16295</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06429</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8636200000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22684</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.21011</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21093</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15074</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8666699999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70286</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09601</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10706</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.1071</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13404</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10478</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52027</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20011</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.64483</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57956</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15268</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73611</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6679700000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.1842</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8650399999999999</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.07378</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.04701</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.06977</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03692</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06848</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12729</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04995</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06056</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18379</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16239</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.23858</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20286</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.27514</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.1689</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.16291</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11936</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12608</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17577</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19333</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17394</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.08654</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67836</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6179</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.56835</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53491</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31268</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30996</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06705</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.45382</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.45777</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.45612</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.45191</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.44575</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84826</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56938</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68843</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.7040599999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65562</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9454400000000001</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75664</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9508</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.16259</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.31205</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.45256</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.4404</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45856</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.5523</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25643</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85099</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.68239</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73426</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70043</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50245</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84414</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8708899999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.22306</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7738200000000001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5797599999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58184</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.63173</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7127899999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58921</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7397400000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61461</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20418</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.18019</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41313</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.18172</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.18127</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10998</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.08458</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20724</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.11208</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19833</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05754</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08851</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.2063</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08998</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54515</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8081799999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80399</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56398</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21848</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84949</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5590599999999999</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55452</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56267</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55389</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52115</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50119</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.4597</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49512</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5201699999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52037</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55743</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17537</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88282</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49358</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17955</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50907</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5695800000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8442799999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79527</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5970299999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8526</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50195</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54422</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17716</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.7008300000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55513</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17603</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54903</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55004</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79943</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79855</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17394</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79849</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.06103</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17483</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17694</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17901</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.1769</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.82359</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73326</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68714</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7318</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83433</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8176</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6171</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8091900000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7587</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13865</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75509</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6093099999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6402599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64054</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6150099999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.70814</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67283</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81765</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70401</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6081</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5309700000000001</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51246</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
